--- a/activity/M03A03/M03A03_ParametroCondicionFrontera.xlsx
+++ b/activity/M03A03/M03A03_ParametroCondicionFrontera.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DE47DE-B997-41C7-921A-59B7C7508CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3721894E-6925-4B72-BC54-37DAE295945D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -610,30 +610,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -678,8 +654,14 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -689,6 +671,24 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -806,7 +806,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="65000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2105,25 +2105,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
       <c r="B4" s="15" t="s">
@@ -2146,14 +2146,14 @@
       <c r="B5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="22">
         <v>5</v>
       </c>
       <c r="D5" s="18">
         <f>Detalle!C10*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="19">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2163,14 +2163,14 @@
       <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="22">
         <v>5</v>
       </c>
       <c r="D6" s="18">
         <f>Detalle!F10*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="19">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2180,14 +2180,14 @@
       <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="22">
         <v>5</v>
       </c>
       <c r="D7" s="18">
         <f>Detalle!I10*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="22"/>
       <c r="F7" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2197,14 +2197,14 @@
       <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="22">
         <v>5</v>
       </c>
       <c r="D8" s="18">
         <f>Detalle!L10*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="30"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2214,14 +2214,14 @@
       <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="22">
         <v>5</v>
       </c>
       <c r="D9" s="18">
         <f>Detalle!O10*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="30"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2231,14 +2231,14 @@
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="22">
         <v>5</v>
       </c>
       <c r="D10" s="18">
         <f>Detalle!R10*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="30"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2248,14 +2248,14 @@
       <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="22">
         <v>5</v>
       </c>
       <c r="D11" s="18">
         <f>Detalle!U10*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="22"/>
       <c r="F11" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2265,14 +2265,14 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="22">
         <v>5</v>
       </c>
       <c r="D12" s="18">
         <f>Detalle!X10*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="30"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2282,14 +2282,14 @@
       <c r="B13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="22">
         <v>5</v>
       </c>
       <c r="D13" s="18">
         <f>Detalle!AA10*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2299,14 +2299,14 @@
       <c r="B14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="22">
         <v>5</v>
       </c>
       <c r="D14" s="18">
         <f>Detalle!AD10*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="30"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2316,14 +2316,14 @@
       <c r="B15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="22">
         <v>5</v>
       </c>
       <c r="D15" s="18">
         <f>Detalle!AG10*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="30"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2333,14 +2333,14 @@
       <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="22">
         <v>5</v>
       </c>
       <c r="D16" s="18">
         <f>Detalle!AJ10*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="30"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2350,52 +2350,52 @@
       <c r="B17" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="22">
         <v>5</v>
       </c>
       <c r="D17" s="18">
         <f>Detalle!AM10*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="30"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="25">
         <v>5</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="26">
         <f>Detalle!AP10*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="35">
+      <c r="E18" s="25"/>
+      <c r="F18" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="29" t="str">
+      <c r="B19" s="37" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A03 en GitHub.</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="20"/>
@@ -2494,96 +2494,96 @@
     </row>
     <row r="2" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5"/>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="24" t="str">
+      <c r="C2" s="41" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="24" t="str">
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="41" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="24" t="str">
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="41" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="24" t="str">
+      <c r="J2" s="42"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="41" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="25"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="24" t="str">
+      <c r="M2" s="42"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="41" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="24" t="str">
+      <c r="P2" s="42"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="41" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="25"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="24" t="str">
+      <c r="S2" s="42"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="41" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="25"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="24" t="str">
+      <c r="V2" s="42"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="41" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="24" t="str">
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="41" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="24" t="str">
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="41" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="24" t="str">
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="41" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="24" t="str">
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="41" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="24" t="str">
+      <c r="AK2" s="42"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="41" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="26"/>
-      <c r="AP2" s="24" t="str">
+      <c r="AN2" s="42"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="41" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="26"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="43"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="28"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2715,399 +2715,399 @@
       <c r="B4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="36">
-        <v>0</v>
-      </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="36">
-        <v>0</v>
-      </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="36">
-        <v>0</v>
-      </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="36">
-        <v>0</v>
-      </c>
-      <c r="M4" s="37"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="36">
-        <v>0</v>
-      </c>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="36">
-        <v>0</v>
-      </c>
-      <c r="S4" s="37"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="36">
-        <v>0</v>
-      </c>
-      <c r="V4" s="37"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="36">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="37"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="37"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="37"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="37"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="37"/>
-      <c r="AR4" s="38"/>
+      <c r="C4" s="28">
+        <v>0</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="28">
+        <v>0</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="28">
+        <v>0</v>
+      </c>
+      <c r="J4" s="29"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="28">
+        <v>0</v>
+      </c>
+      <c r="M4" s="29"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="28">
+        <v>0</v>
+      </c>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="28">
+        <v>0</v>
+      </c>
+      <c r="S4" s="29"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="28">
+        <v>0</v>
+      </c>
+      <c r="V4" s="29"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="28">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="29"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="29"/>
+      <c r="AL4" s="30"/>
+      <c r="AM4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="29"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="28">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="30"/>
     </row>
     <row r="5" spans="1:44" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="36"/>
-      <c r="AE5" s="37"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="37"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="36"/>
-      <c r="AN5" s="37"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="36"/>
-      <c r="AQ5" s="37"/>
-      <c r="AR5" s="38"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="29"/>
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="29"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="29"/>
+      <c r="AR5" s="30"/>
     </row>
     <row r="6" spans="1:44" ht="107.65" x14ac:dyDescent="0.45">
       <c r="B6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="36"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="36"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="36"/>
-      <c r="AK6" s="37"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="36"/>
-      <c r="AN6" s="37"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="36"/>
-      <c r="AQ6" s="37"/>
-      <c r="AR6" s="38"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="30"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="30"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="30"/>
     </row>
     <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="36"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="36"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="36"/>
-      <c r="AN7" s="37"/>
-      <c r="AO7" s="38"/>
-      <c r="AP7" s="36"/>
-      <c r="AQ7" s="37"/>
-      <c r="AR7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="30"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="30"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="30"/>
     </row>
     <row r="8" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="36"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="36"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="36"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="38"/>
-      <c r="AM8" s="36"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="36"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="38"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="30"/>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="29"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="30"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="29"/>
+      <c r="AR8" s="30"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="42"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="42"/>
-      <c r="AD9" s="40"/>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="42"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="40"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="42"/>
-      <c r="AM9" s="40"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="42"/>
-      <c r="AP9" s="40"/>
-      <c r="AQ9" s="41"/>
-      <c r="AR9" s="42"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="33"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="32"/>
+      <c r="AK9" s="33"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="32"/>
+      <c r="AN9" s="33"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="32"/>
+      <c r="AQ9" s="33"/>
+      <c r="AR9" s="34"/>
     </row>
     <row r="10" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="38">
         <f>AVERAGE(C4:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="44">
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="38">
         <f>AVERAGE(F4:F9)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="44">
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="38">
         <f>AVERAGE(I4:I9)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="45"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="44">
+      <c r="J10" s="39"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="38">
         <f>AVERAGE(L4:L9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="45"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="44">
+      <c r="M10" s="39"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="38">
         <f>AVERAGE(O4:O9)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="44">
+      <c r="P10" s="39"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="38">
         <f>AVERAGE(R4:R9)</f>
         <v>0</v>
       </c>
-      <c r="S10" s="45"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="44">
+      <c r="S10" s="39"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="38">
         <f>AVERAGE(U4:U9)</f>
         <v>0</v>
       </c>
-      <c r="V10" s="45"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="44">
+      <c r="V10" s="39"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="38">
         <f>AVERAGE(X4:X9)</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="44">
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="38">
         <f>AVERAGE(AA4:AA9)</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="46"/>
-      <c r="AD10" s="44">
+      <c r="AB10" s="39"/>
+      <c r="AC10" s="40"/>
+      <c r="AD10" s="38">
         <f>AVERAGE(AD4:AD9)</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="46"/>
-      <c r="AG10" s="44">
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="40"/>
+      <c r="AG10" s="38">
         <f>AVERAGE(AG4:AG9)</f>
         <v>0</v>
       </c>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46"/>
-      <c r="AJ10" s="44">
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="40"/>
+      <c r="AJ10" s="38">
         <f>AVERAGE(AJ4:AJ9)</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="46"/>
-      <c r="AM10" s="44">
+      <c r="AK10" s="39"/>
+      <c r="AL10" s="40"/>
+      <c r="AM10" s="38">
         <f>AVERAGE(AM4:AM9)</f>
         <v>0</v>
       </c>
-      <c r="AN10" s="45"/>
-      <c r="AO10" s="46"/>
-      <c r="AP10" s="44">
+      <c r="AN10" s="39"/>
+      <c r="AO10" s="40"/>
+      <c r="AP10" s="38">
         <f>AVERAGE(AP4:AP9)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="45"/>
-      <c r="AR10" s="46"/>
+      <c r="AQ10" s="39"/>
+      <c r="AR10" s="40"/>
     </row>
     <row r="11" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="4"/>
@@ -4461,20 +4461,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="AA10:AC10"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
-    <mergeCell ref="AM10:AO10"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AM2:AO2"/>
@@ -4490,6 +4476,20 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="X10:Z10"/>
+    <mergeCell ref="AA10:AC10"/>
+    <mergeCell ref="AD10:AF10"/>
+    <mergeCell ref="AG10:AI10"/>
+    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="AM10:AO10"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
